--- a/05 Others/2026.1 Avaliação Projetos/Turma Introdução a Programação - WYD6376 Turma 3001 PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Introdução a Programação - WYD6376 Turma 3001 PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EB9BA8-9E00-4874-A72D-299668B68B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04204204-682D-44E7-9670-67760EA714FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
   <si>
     <t>ALUNO</t>
   </si>
@@ -147,7 +147,19 @@
     <t>Cad Bloco de Notas</t>
   </si>
   <si>
-    <t>???</t>
+    <t>não GitHub</t>
+  </si>
+  <si>
+    <t>https://github.com/MairoCruz?tab=repositories</t>
+  </si>
+  <si>
+    <t>não apresentou</t>
+  </si>
+  <si>
+    <t>repo privado</t>
+  </si>
+  <si>
+    <t>não fez</t>
   </si>
 </sst>
 </file>
@@ -190,7 +202,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,8 +227,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -383,12 +401,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -436,6 +463,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -830,11 +875,16 @@
       <c r="E2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>4</v>
+      <c r="F2" s="20">
+        <v>0</v>
       </c>
       <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
+      <c r="H2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -906,11 +956,16 @@
       <c r="E5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>4</v>
+      <c r="F5" s="17">
+        <v>0</v>
       </c>
       <c r="G5" s="12"/>
-      <c r="H5" s="13"/>
+      <c r="H5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
@@ -940,27 +995,30 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="B7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="12">
         <v>0.9</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1"/>
+      <c r="F7" s="17">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12"/>
       <c r="H7" s="7" t="s">
         <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -1017,28 +1075,31 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:9" ht="63" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="B10" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="12">
         <v>0.9</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="17">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13" t="s">
         <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1057,38 +1118,42 @@
       <c r="E11" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>4</v>
+      <c r="F11" s="17">
+        <v>0</v>
       </c>
       <c r="G11" s="12"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="H11" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="B12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="19">
         <v>0.2</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
+      <c r="F12" s="19">
+        <v>1</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="I12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -1104,16 +1169,13 @@
       <c r="E13" s="1">
         <v>0.7</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>4</v>
+      <c r="F13" s="1">
+        <v>2</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I13" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="14" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -1131,15 +1193,15 @@
       <c r="E14" s="6">
         <v>0.9</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>4</v>
+      <c r="F14" s="6">
+        <v>1</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="8" t="s">
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1154,6 +1216,7 @@
     <hyperlink ref="H6" r:id="rId3" xr:uid="{B09F1058-3EEF-4598-9BE1-72F510256565}"/>
     <hyperlink ref="H14" r:id="rId4" xr:uid="{F41FECF8-FA5B-478E-B55F-FB387C1944F9}"/>
     <hyperlink ref="H7" r:id="rId5" xr:uid="{E59F5675-737A-4AF3-A919-99F3459ACB3C}"/>
+    <hyperlink ref="H12" r:id="rId6" xr:uid="{5FE31AA5-DBA2-46DE-81F2-57008A8177CA}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/05 Others/2026.1 Avaliação Projetos/Turma Introdução a Programação - WYD6376 Turma 3001 PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Introdução a Programação - WYD6376 Turma 3001 PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04204204-682D-44E7-9670-67760EA714FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39064938-0D19-43F5-8659-0E4FFAAD9ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -150,16 +150,16 @@
     <t>não GitHub</t>
   </si>
   <si>
-    <t>https://github.com/MairoCruz?tab=repositories</t>
-  </si>
-  <si>
     <t>não apresentou</t>
   </si>
   <si>
-    <t>repo privado</t>
-  </si>
-  <si>
     <t>não fez</t>
+  </si>
+  <si>
+    <t>https://github.com/MairoCruz/Projeto</t>
+  </si>
+  <si>
+    <t>atrasado</t>
   </si>
 </sst>
 </file>
@@ -415,7 +415,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -466,12 +466,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -875,7 +869,7 @@
       <c r="E2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="18">
         <v>0</v>
       </c>
       <c r="G2" s="15"/>
@@ -883,7 +877,7 @@
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -963,8 +957,8 @@
       <c r="H5" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>40</v>
+      <c r="I5" s="20" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -1018,7 +1012,7 @@
         <v>29</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -1099,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1127,30 +1121,30 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="19" t="s">
+      <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="1">
         <v>0.2</v>
       </c>
-      <c r="F12" s="19">
-        <v>1</v>
-      </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="21" t="s">
-        <v>37</v>
+      <c r="F12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
@@ -1194,14 +1188,14 @@
         <v>0.9</v>
       </c>
       <c r="F14" s="6">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="8" t="s">
         <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
